--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateTemplate.xlsx
@@ -719,11 +719,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
@@ -734,12 +731,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1087,74 +1078,74 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" customHeight="1" spans="1:17">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6"/>
+      <c r="Q1" s="4"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:17">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="7"/>
+    <row r="2" s="1" customFormat="1" spans="1:17">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateTemplate.xlsx
@@ -87,13 +87,20 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="10"/>
@@ -574,153 +581,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
@@ -729,8 +739,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1078,74 +1091,74 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" customHeight="1" spans="1:17">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4"/>
+      <c r="Q1" s="5"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:17">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="4"/>
+    <row r="2" s="2" customFormat="1" spans="1:17">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateTemplate.xlsx
@@ -56,7 +56,19 @@
     <t>区域</t>
   </si>
   <si>
-    <t>收货人</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>收货人</t>
+    </r>
   </si>
   <si>
     <t>邮编</t>
@@ -87,7 +99,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -108,6 +120,13 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -259,6 +278,13 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="33">
@@ -581,152 +607,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -740,6 +766,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1118,7 +1147,7 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1139,7 +1168,7 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5"/>
+      <c r="Q1" s="6"/>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:17">
       <c r="A2" s="4"/>
@@ -1158,7 +1187,7 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="6"/>
+      <c r="Q2" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/b2cCustomerUpdateTemplate.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="客户信息" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>销售单号</t>
   </si>
@@ -57,6 +57,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="major"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -78,6 +85,9 @@
   </si>
   <si>
     <t>收件人税号</t>
+  </si>
+  <si>
+    <t>IE号</t>
   </si>
   <si>
     <t>收货地址1</t>
@@ -1096,7 +1106,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
@@ -1110,16 +1120,16 @@
     <col min="11" max="11" width="19.875" customWidth="1"/>
     <col min="12" max="12" width="15.75" customWidth="1"/>
     <col min="13" max="13" width="15.625" customWidth="1"/>
-    <col min="14" max="14" width="16.25" customWidth="1"/>
-    <col min="15" max="15" width="16.625" customWidth="1"/>
-    <col min="16" max="16" width="22.25" customWidth="1"/>
-    <col min="17" max="17" width="17.25" customWidth="1"/>
-    <col min="18" max="18" width="18.25" customWidth="1"/>
-    <col min="19" max="19" width="16.625" customWidth="1"/>
-    <col min="20" max="20" width="14.25" customWidth="1"/>
+    <col min="14" max="15" width="16.25" customWidth="1"/>
+    <col min="16" max="16" width="16.625" customWidth="1"/>
+    <col min="17" max="17" width="22.25" customWidth="1"/>
+    <col min="18" max="18" width="17.25" customWidth="1"/>
+    <col min="19" max="19" width="18.25" customWidth="1"/>
+    <col min="20" max="20" width="16.625" customWidth="1"/>
+    <col min="21" max="21" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" customHeight="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="15" customHeight="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1168,9 +1178,12 @@
       <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6"/>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="6"/>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:17">
+    <row r="2" s="2" customFormat="1" spans="1:18">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1187,7 +1200,8 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="7"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
